--- a/assets/templates.xlsx
+++ b/assets/templates.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Claude Code\Auftragsdoku FlexPos NFK + BBA\_deploy\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Claude Code\Auftragsdoku FlexPos NFK\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E5F2D2-40DC-489E-A4A3-7A0000027D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0E2A6C-6219-4430-8898-F0552E6B10FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25905" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NFK Vollverkabelung" sheetId="1" r:id="rId1"/>
@@ -35,6 +35,9 @@
     <t>Pflichtanzahl</t>
   </si>
   <si>
+    <t>Kassenzone</t>
+  </si>
+  <si>
     <t>01_Maengel</t>
   </si>
   <si>
@@ -1347,9 +1350,6 @@
   </si>
   <si>
     <t>HGA Dose Totale</t>
-  </si>
-  <si>
-    <t>Kassenzone</t>
   </si>
 </sst>
 </file>
@@ -1805,13 +1805,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>442</v>
+        <v>4</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D2" s="8">
         <v>1</v>
@@ -1821,7 +1821,7 @@
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" s="8">
         <v>1</v>
@@ -1831,7 +1831,7 @@
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D4" s="8">
         <v>1</v>
@@ -1841,7 +1841,7 @@
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D5" s="8">
         <v>1</v>
@@ -1851,7 +1851,7 @@
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6" s="8">
         <v>1</v>
@@ -1861,7 +1861,7 @@
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D7" s="8">
         <v>1</v>
@@ -1871,7 +1871,7 @@
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D8" s="8">
         <v>1</v>
@@ -1881,7 +1881,7 @@
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D9" s="8">
         <v>1</v>
@@ -1891,7 +1891,7 @@
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D10" s="8">
         <v>3</v>
@@ -1900,10 +1900,10 @@
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" s="5">
         <v>1</v>
@@ -1913,7 +1913,7 @@
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" s="5">
         <v>1</v>
@@ -1923,7 +1923,7 @@
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" s="5">
         <v>1</v>
@@ -1932,10 +1932,10 @@
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" s="5">
         <v>1</v>
@@ -1945,7 +1945,7 @@
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" s="5">
         <v>1</v>
@@ -1955,7 +1955,7 @@
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D16" s="5">
         <v>1</v>
@@ -1964,10 +1964,10 @@
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D17" s="5">
         <v>1</v>
@@ -1977,7 +1977,7 @@
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D18" s="5">
         <v>1</v>
@@ -1987,7 +1987,7 @@
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" s="5">
         <v>1</v>
@@ -1996,10 +1996,10 @@
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D20" s="5">
         <v>1</v>
@@ -2009,7 +2009,7 @@
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D21" s="5">
         <v>1</v>
@@ -2019,7 +2019,7 @@
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D22" s="5">
         <v>1</v>
@@ -2028,10 +2028,10 @@
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D23" s="5">
         <v>1</v>
@@ -2041,7 +2041,7 @@
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D24" s="5">
         <v>1</v>
@@ -2051,7 +2051,7 @@
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D25" s="5">
         <v>1</v>
@@ -2060,10 +2060,10 @@
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D26" s="5">
         <v>1</v>
@@ -2073,7 +2073,7 @@
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27" s="5">
         <v>1</v>
@@ -2083,7 +2083,7 @@
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D28" s="5">
         <v>1</v>
@@ -2092,10 +2092,10 @@
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D29" s="5">
         <v>1</v>
@@ -2105,7 +2105,7 @@
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D30" s="5">
         <v>1</v>
@@ -2115,7 +2115,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D31" s="5">
         <v>1</v>
@@ -2124,10 +2124,10 @@
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D32" s="5">
         <v>1</v>
@@ -2137,7 +2137,7 @@
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D33" s="5">
         <v>1</v>
@@ -2147,7 +2147,7 @@
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D34" s="5">
         <v>1</v>
@@ -2156,10 +2156,10 @@
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D35" s="5">
         <v>1</v>
@@ -2169,7 +2169,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D36" s="5">
         <v>1</v>
@@ -2179,7 +2179,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D37" s="5">
         <v>1</v>
@@ -2188,10 +2188,10 @@
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D38" s="5">
         <v>1</v>
@@ -2201,7 +2201,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D39" s="5">
         <v>1</v>
@@ -2210,10 +2210,10 @@
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D40" s="5">
         <v>1</v>
@@ -2223,7 +2223,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D41" s="5">
         <v>1</v>
@@ -2232,10 +2232,10 @@
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D42" s="5">
         <v>1</v>
@@ -2245,7 +2245,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D43" s="5">
         <v>1</v>
@@ -2254,10 +2254,10 @@
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D44" s="5">
         <v>1</v>
@@ -2267,7 +2267,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D45" s="5">
         <v>1</v>
@@ -2276,10 +2276,10 @@
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D46" s="5">
         <v>1</v>
@@ -2289,7 +2289,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D47" s="5">
         <v>1</v>
@@ -2298,10 +2298,10 @@
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D48" s="5">
         <v>1</v>
@@ -2311,7 +2311,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D49" s="5">
         <v>1</v>
@@ -2320,10 +2320,10 @@
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D50" s="5">
         <v>1</v>
@@ -2333,7 +2333,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D51" s="5">
         <v>1</v>
@@ -2342,10 +2342,10 @@
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D52" s="5">
         <v>1</v>
@@ -2355,7 +2355,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D53" s="5">
         <v>1</v>
@@ -2364,10 +2364,10 @@
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D54" s="5">
         <v>1</v>
@@ -2377,7 +2377,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D55" s="5">
         <v>1</v>
@@ -2386,10 +2386,10 @@
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D56" s="5">
         <v>1</v>
@@ -2399,7 +2399,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D57" s="5">
         <v>1</v>
@@ -2409,7 +2409,7 @@
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D58" s="5">
         <v>1</v>
@@ -2419,7 +2419,7 @@
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D59" s="5">
         <v>1</v>
@@ -2428,10 +2428,10 @@
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D60" s="5">
         <v>1</v>
@@ -2441,7 +2441,7 @@
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D61" s="5">
         <v>1</v>
@@ -2451,7 +2451,7 @@
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D62" s="5">
         <v>1</v>
@@ -2461,7 +2461,7 @@
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D63" s="5">
         <v>1</v>
@@ -2471,7 +2471,7 @@
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D64" s="5">
         <v>1</v>
@@ -2481,7 +2481,7 @@
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D65" s="5">
         <v>1</v>
@@ -2491,7 +2491,7 @@
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D66" s="5">
         <v>1</v>
@@ -2501,7 +2501,7 @@
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D67" s="5">
         <v>1</v>
@@ -2511,7 +2511,7 @@
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D68" s="5">
         <v>1</v>
@@ -2521,7 +2521,7 @@
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D69" s="5">
         <v>1</v>
@@ -2529,11 +2529,11 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D70" s="5">
         <v>1</v>
@@ -2543,7 +2543,7 @@
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D71" s="5">
         <v>1</v>
@@ -2553,7 +2553,7 @@
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D72" s="5">
         <v>1</v>
@@ -2563,7 +2563,7 @@
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D73" s="5">
         <v>1</v>
@@ -2573,7 +2573,7 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D74" s="5">
         <v>1</v>
@@ -2583,7 +2583,7 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D75" s="5">
         <v>1</v>
@@ -2593,7 +2593,7 @@
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D76" s="5">
         <v>1</v>
@@ -2603,7 +2603,7 @@
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="7" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D77" s="5">
         <v>1</v>
@@ -2613,7 +2613,7 @@
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="7" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D78" s="5">
         <v>1</v>
@@ -2623,7 +2623,7 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D79" s="5">
         <v>3</v>
@@ -2631,11 +2631,11 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D80" s="5">
         <v>1</v>
@@ -2645,7 +2645,7 @@
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D81" s="5">
         <v>1</v>
@@ -2655,7 +2655,7 @@
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D82" s="5">
         <v>1</v>
@@ -2665,7 +2665,7 @@
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D83" s="5">
         <v>1</v>
@@ -2675,7 +2675,7 @@
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D84" s="5">
         <v>1</v>
@@ -2685,7 +2685,7 @@
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D85" s="5">
         <v>1</v>
@@ -2695,7 +2695,7 @@
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D86" s="5">
         <v>1</v>
@@ -2705,7 +2705,7 @@
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D87" s="5">
         <v>1</v>
@@ -2715,7 +2715,7 @@
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D88" s="5">
         <v>1</v>
@@ -2725,7 +2725,7 @@
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D89" s="5">
         <v>3</v>
@@ -2735,7 +2735,7 @@
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D90" s="5">
         <v>1</v>
@@ -2745,7 +2745,7 @@
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D91" s="5">
         <v>3</v>
@@ -2753,13 +2753,13 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D92" s="5">
         <v>1</v>
@@ -2769,7 +2769,7 @@
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D93" s="5">
         <v>1</v>
@@ -2779,7 +2779,7 @@
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D94" s="5">
         <v>1</v>
@@ -2789,7 +2789,7 @@
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D95" s="5">
         <v>1</v>
@@ -2799,7 +2799,7 @@
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D96" s="5">
         <v>1</v>
@@ -2809,7 +2809,7 @@
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D97" s="5">
         <v>1</v>
@@ -2819,7 +2819,7 @@
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D98" s="5">
         <v>1</v>
@@ -2829,7 +2829,7 @@
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D99" s="5">
         <v>1</v>
@@ -2839,7 +2839,7 @@
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D100" s="5">
         <v>1</v>
@@ -2849,7 +2849,7 @@
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D101" s="5">
         <v>1</v>
@@ -2859,7 +2859,7 @@
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D102" s="5">
         <v>1</v>
@@ -2869,7 +2869,7 @@
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D103" s="5">
         <v>1</v>
@@ -2879,7 +2879,7 @@
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D104" s="5">
         <v>1</v>
@@ -2889,7 +2889,7 @@
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D105" s="5">
         <v>3</v>
@@ -2898,10 +2898,10 @@
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="4"/>
       <c r="B106" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D106" s="5">
         <v>1</v>
@@ -2911,7 +2911,7 @@
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D107" s="5">
         <v>1</v>
@@ -2921,7 +2921,7 @@
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D108" s="5">
         <v>1</v>
@@ -2931,7 +2931,7 @@
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D109" s="5">
         <v>1</v>
@@ -2941,7 +2941,7 @@
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D110" s="5">
         <v>1</v>
@@ -2951,7 +2951,7 @@
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D111" s="5">
         <v>1</v>
@@ -2961,7 +2961,7 @@
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D112" s="5">
         <v>1</v>
@@ -2971,7 +2971,7 @@
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D113" s="5">
         <v>1</v>
@@ -2981,7 +2981,7 @@
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D114" s="5">
         <v>1</v>
@@ -2990,10 +2990,10 @@
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="4"/>
       <c r="B115" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D115" s="5">
         <v>1</v>
@@ -3003,7 +3003,7 @@
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D116" s="5">
         <v>1</v>
@@ -3013,7 +3013,7 @@
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D117" s="5">
         <v>1</v>
@@ -3023,7 +3023,7 @@
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D118" s="5">
         <v>1</v>
@@ -3031,11 +3031,11 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D119" s="5">
         <v>1</v>
@@ -3045,7 +3045,7 @@
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D120" s="5">
         <v>1</v>
@@ -3055,7 +3055,7 @@
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D121" s="5">
         <v>1</v>
@@ -3065,7 +3065,7 @@
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D122" s="5">
         <v>1</v>
@@ -3075,7 +3075,7 @@
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D123" s="5">
         <v>1</v>
@@ -3085,7 +3085,7 @@
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D124" s="5">
         <v>1</v>
@@ -3095,7 +3095,7 @@
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D125" s="5">
         <v>3</v>
@@ -3103,11 +3103,11 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B126" s="4"/>
       <c r="C126" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D126" s="5">
         <v>1</v>
@@ -3117,7 +3117,7 @@
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D127" s="5">
         <v>1</v>
@@ -3127,7 +3127,7 @@
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D128" s="5">
         <v>1</v>
@@ -3137,7 +3137,7 @@
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D129" s="5">
         <v>1</v>
@@ -3147,7 +3147,7 @@
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D130" s="5">
         <v>3</v>
@@ -3155,13 +3155,13 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D131" s="5">
         <v>1</v>
@@ -3171,7 +3171,7 @@
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D132" s="5">
         <v>1</v>
@@ -3181,7 +3181,7 @@
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D133" s="5">
         <v>1</v>
@@ -3191,7 +3191,7 @@
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D134" s="5">
         <v>1</v>
@@ -3201,7 +3201,7 @@
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D135" s="5">
         <v>1</v>
@@ -3211,7 +3211,7 @@
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D136" s="5">
         <v>1</v>
@@ -3221,7 +3221,7 @@
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D137" s="5">
         <v>1</v>
@@ -3230,10 +3230,10 @@
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="4"/>
       <c r="B138" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D138" s="5">
         <v>1</v>
@@ -3243,7 +3243,7 @@
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D139" s="5">
         <v>1</v>
@@ -3253,7 +3253,7 @@
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D140" s="5">
         <v>1</v>
@@ -3263,7 +3263,7 @@
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D141" s="5">
         <v>1</v>
@@ -3273,7 +3273,7 @@
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D142" s="5">
         <v>1</v>
@@ -3283,7 +3283,7 @@
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D143" s="5">
         <v>1</v>
@@ -3293,7 +3293,7 @@
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D144" s="5">
         <v>1</v>
@@ -3302,10 +3302,10 @@
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="4"/>
       <c r="B145" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D145" s="5">
         <v>1</v>
@@ -3315,7 +3315,7 @@
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D146" s="5">
         <v>1</v>
@@ -3325,7 +3325,7 @@
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D147" s="5">
         <v>1</v>
@@ -3335,7 +3335,7 @@
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D148" s="5">
         <v>1</v>
@@ -3345,7 +3345,7 @@
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D149" s="5">
         <v>1</v>
@@ -3355,7 +3355,7 @@
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D150" s="5">
         <v>1</v>
@@ -3365,7 +3365,7 @@
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D151" s="5">
         <v>1</v>
@@ -3374,10 +3374,10 @@
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="4"/>
       <c r="B152" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D152" s="5">
         <v>1</v>
@@ -3387,7 +3387,7 @@
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D153" s="5">
         <v>1</v>
@@ -3397,7 +3397,7 @@
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D154" s="5">
         <v>1</v>
@@ -3407,7 +3407,7 @@
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D155" s="5">
         <v>1</v>
@@ -3417,7 +3417,7 @@
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D156" s="5">
         <v>1</v>
@@ -3427,7 +3427,7 @@
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D157" s="5">
         <v>1</v>
@@ -3437,7 +3437,7 @@
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D158" s="5">
         <v>1</v>
@@ -3446,10 +3446,10 @@
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="4"/>
       <c r="B159" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D159" s="5">
         <v>1</v>
@@ -3459,7 +3459,7 @@
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D160" s="5">
         <v>1</v>
@@ -3469,7 +3469,7 @@
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D161" s="5">
         <v>1</v>
@@ -3479,7 +3479,7 @@
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D162" s="5">
         <v>1</v>
@@ -3489,7 +3489,7 @@
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D163" s="5">
         <v>1</v>
@@ -3499,7 +3499,7 @@
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D164" s="5">
         <v>1</v>
@@ -3509,7 +3509,7 @@
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D165" s="5">
         <v>1</v>
@@ -3518,10 +3518,10 @@
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="4"/>
       <c r="B166" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D166" s="5">
         <v>1</v>
@@ -3531,7 +3531,7 @@
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D167" s="5">
         <v>1</v>
@@ -3541,7 +3541,7 @@
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D168" s="5">
         <v>1</v>
@@ -3551,7 +3551,7 @@
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D169" s="5">
         <v>1</v>
@@ -3561,7 +3561,7 @@
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D170" s="5">
         <v>1</v>
@@ -3571,7 +3571,7 @@
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D171" s="5">
         <v>1</v>
@@ -3581,7 +3581,7 @@
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D172" s="5">
         <v>1</v>
@@ -3590,10 +3590,10 @@
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="4"/>
       <c r="B173" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D173" s="5">
         <v>1</v>
@@ -3603,7 +3603,7 @@
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D174" s="5">
         <v>1</v>
@@ -3613,7 +3613,7 @@
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D175" s="5">
         <v>1</v>
@@ -3623,7 +3623,7 @@
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D176" s="5">
         <v>1</v>
@@ -3633,7 +3633,7 @@
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D177" s="5">
         <v>1</v>
@@ -3643,7 +3643,7 @@
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D178" s="5">
         <v>1</v>
@@ -3653,7 +3653,7 @@
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D179" s="5">
         <v>1</v>
@@ -3662,10 +3662,10 @@
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="4"/>
       <c r="B180" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C180" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D180" s="5">
         <v>1</v>
@@ -3675,7 +3675,7 @@
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D181" s="5">
         <v>1</v>
@@ -3685,7 +3685,7 @@
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D182" s="5">
         <v>1</v>
@@ -3695,7 +3695,7 @@
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D183" s="5">
         <v>1</v>
@@ -3705,7 +3705,7 @@
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D184" s="5">
         <v>1</v>
@@ -3715,7 +3715,7 @@
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D185" s="5">
         <v>1</v>
@@ -3725,7 +3725,7 @@
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D186" s="5">
         <v>1</v>
@@ -3734,10 +3734,10 @@
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="4"/>
       <c r="B187" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D187" s="5">
         <v>1</v>
@@ -3747,7 +3747,7 @@
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D188" s="5">
         <v>1</v>
@@ -3757,7 +3757,7 @@
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D189" s="5">
         <v>1</v>
@@ -3767,7 +3767,7 @@
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D190" s="5">
         <v>1</v>
@@ -3777,7 +3777,7 @@
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D191" s="5">
         <v>1</v>
@@ -3787,7 +3787,7 @@
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D192" s="5">
         <v>1</v>
@@ -3797,7 +3797,7 @@
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D193" s="5">
         <v>1</v>
@@ -3806,10 +3806,10 @@
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="4"/>
       <c r="B194" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D194" s="5">
         <v>1</v>
@@ -3819,7 +3819,7 @@
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D195" s="5">
         <v>1</v>
@@ -3829,7 +3829,7 @@
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D196" s="5">
         <v>1</v>
@@ -3839,7 +3839,7 @@
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D197" s="5">
         <v>1</v>
@@ -3849,7 +3849,7 @@
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D198" s="5">
         <v>1</v>
@@ -3859,7 +3859,7 @@
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D199" s="5">
         <v>1</v>
@@ -3869,7 +3869,7 @@
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D200" s="5">
         <v>1</v>
@@ -3878,10 +3878,10 @@
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" s="4"/>
       <c r="B201" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D201" s="5">
         <v>1</v>
@@ -3891,7 +3891,7 @@
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D202" s="5">
         <v>1</v>
@@ -3901,7 +3901,7 @@
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D203" s="5">
         <v>1</v>
@@ -3911,7 +3911,7 @@
       <c r="A204" s="4"/>
       <c r="B204" s="4"/>
       <c r="C204" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D204" s="5">
         <v>1</v>
@@ -3921,7 +3921,7 @@
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
       <c r="C205" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D205" s="5">
         <v>1</v>
@@ -3931,7 +3931,7 @@
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D206" s="5">
         <v>1</v>
@@ -3941,7 +3941,7 @@
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D207" s="5">
         <v>1</v>
@@ -3950,10 +3950,10 @@
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" s="4"/>
       <c r="B208" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D208" s="5">
         <v>1</v>
@@ -3963,7 +3963,7 @@
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D209" s="5">
         <v>1</v>
@@ -3973,7 +3973,7 @@
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D210" s="5">
         <v>1</v>
@@ -3983,7 +3983,7 @@
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D211" s="5">
         <v>1</v>
@@ -3993,7 +3993,7 @@
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D212" s="5">
         <v>1</v>
@@ -4003,7 +4003,7 @@
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D213" s="5">
         <v>1</v>
@@ -4013,7 +4013,7 @@
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D214" s="5">
         <v>1</v>
@@ -4022,10 +4022,10 @@
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" s="4"/>
       <c r="B215" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D215" s="5">
         <v>1</v>
@@ -4035,7 +4035,7 @@
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D216" s="5">
         <v>1</v>
@@ -4045,7 +4045,7 @@
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D217" s="5">
         <v>1</v>
@@ -4055,7 +4055,7 @@
       <c r="A218" s="4"/>
       <c r="B218" s="4"/>
       <c r="C218" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D218" s="5">
         <v>1</v>
@@ -4065,7 +4065,7 @@
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D219" s="5">
         <v>1</v>
@@ -4075,7 +4075,7 @@
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D220" s="5">
         <v>1</v>
@@ -4085,7 +4085,7 @@
       <c r="A221" s="4"/>
       <c r="B221" s="4"/>
       <c r="C221" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D221" s="5">
         <v>1</v>
@@ -4094,10 +4094,10 @@
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" s="4"/>
       <c r="B222" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C222" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D222" s="5">
         <v>1</v>
@@ -4107,7 +4107,7 @@
       <c r="A223" s="4"/>
       <c r="B223" s="4"/>
       <c r="C223" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D223" s="5">
         <v>1</v>
@@ -4117,7 +4117,7 @@
       <c r="A224" s="4"/>
       <c r="B224" s="4"/>
       <c r="C224" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D224" s="5">
         <v>1</v>
@@ -4127,7 +4127,7 @@
       <c r="A225" s="4"/>
       <c r="B225" s="4"/>
       <c r="C225" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D225" s="5">
         <v>1</v>
@@ -4137,7 +4137,7 @@
       <c r="A226" s="4"/>
       <c r="B226" s="4"/>
       <c r="C226" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D226" s="5">
         <v>1</v>
@@ -4147,7 +4147,7 @@
       <c r="A227" s="4"/>
       <c r="B227" s="4"/>
       <c r="C227" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D227" s="5">
         <v>1</v>
@@ -4157,7 +4157,7 @@
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D228" s="5">
         <v>1</v>
@@ -4166,10 +4166,10 @@
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" s="4"/>
       <c r="B229" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D229" s="5">
         <v>1</v>
@@ -4179,7 +4179,7 @@
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D230" s="5">
         <v>1</v>
@@ -4189,7 +4189,7 @@
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D231" s="5">
         <v>1</v>
@@ -4199,7 +4199,7 @@
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D232" s="5">
         <v>1</v>
@@ -4209,7 +4209,7 @@
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D233" s="5">
         <v>1</v>
@@ -4219,7 +4219,7 @@
       <c r="A234" s="4"/>
       <c r="B234" s="4"/>
       <c r="C234" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D234" s="5">
         <v>1</v>
@@ -4229,7 +4229,7 @@
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D235" s="5">
         <v>1</v>
@@ -4238,10 +4238,10 @@
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="4"/>
       <c r="B236" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C236" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D236" s="5">
         <v>1</v>
@@ -4251,7 +4251,7 @@
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D237" s="5">
         <v>1</v>
@@ -4261,7 +4261,7 @@
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D238" s="5">
         <v>1</v>
@@ -4271,7 +4271,7 @@
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D239" s="5">
         <v>1</v>
@@ -4281,7 +4281,7 @@
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D240" s="5">
         <v>1</v>
@@ -4291,7 +4291,7 @@
       <c r="A241" s="4"/>
       <c r="B241" s="4"/>
       <c r="C241" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D241" s="5">
         <v>1</v>
@@ -4301,7 +4301,7 @@
       <c r="A242" s="4"/>
       <c r="B242" s="4"/>
       <c r="C242" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D242" s="5">
         <v>1</v>
@@ -4309,13 +4309,13 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C243" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D243" s="5">
         <v>1</v>
@@ -4325,7 +4325,7 @@
       <c r="A244" s="4"/>
       <c r="B244" s="4"/>
       <c r="C244" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D244" s="5">
         <v>1</v>
@@ -4335,7 +4335,7 @@
       <c r="A245" s="4"/>
       <c r="B245" s="4"/>
       <c r="C245" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D245" s="5">
         <v>1</v>
@@ -4345,7 +4345,7 @@
       <c r="A246" s="4"/>
       <c r="B246" s="4"/>
       <c r="C246" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D246" s="5">
         <v>1</v>
@@ -4355,7 +4355,7 @@
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D247" s="5">
         <v>1</v>
@@ -4365,7 +4365,7 @@
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D248" s="5">
         <v>1</v>
@@ -4375,7 +4375,7 @@
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D249" s="5">
         <v>1</v>
@@ -4385,7 +4385,7 @@
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D250" s="5">
         <v>1</v>
@@ -4395,7 +4395,7 @@
       <c r="A251" s="4"/>
       <c r="B251" s="4"/>
       <c r="C251" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D251" s="5">
         <v>1</v>
@@ -4405,7 +4405,7 @@
       <c r="A252" s="4"/>
       <c r="B252" s="4"/>
       <c r="C252" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D252" s="5">
         <v>3</v>
@@ -4414,10 +4414,10 @@
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" s="4"/>
       <c r="B253" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C253" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D253" s="5">
         <v>1</v>
@@ -4427,7 +4427,7 @@
       <c r="A254" s="4"/>
       <c r="B254" s="4"/>
       <c r="C254" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D254" s="5">
         <v>1</v>
@@ -4437,7 +4437,7 @@
       <c r="A255" s="4"/>
       <c r="B255" s="4"/>
       <c r="C255" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D255" s="5">
         <v>1</v>
@@ -4447,7 +4447,7 @@
       <c r="A256" s="4"/>
       <c r="B256" s="4"/>
       <c r="C256" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D256" s="5">
         <v>1</v>
@@ -4457,7 +4457,7 @@
       <c r="A257" s="4"/>
       <c r="B257" s="4"/>
       <c r="C257" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D257" s="5">
         <v>1</v>
@@ -4465,13 +4465,13 @@
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C258" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D258" s="5">
         <v>1</v>
@@ -4481,7 +4481,7 @@
       <c r="A259" s="4"/>
       <c r="B259" s="4"/>
       <c r="C259" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D259" s="5">
         <v>1</v>
@@ -4491,7 +4491,7 @@
       <c r="A260" s="4"/>
       <c r="B260" s="4"/>
       <c r="C260" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D260" s="5">
         <v>1</v>
@@ -4501,7 +4501,7 @@
       <c r="A261" s="4"/>
       <c r="B261" s="4"/>
       <c r="C261" s="7" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D261" s="5">
         <v>1</v>
@@ -4511,7 +4511,7 @@
       <c r="A262" s="4"/>
       <c r="B262" s="4"/>
       <c r="C262" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D262" s="5">
         <v>1</v>
@@ -4520,10 +4520,10 @@
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="4"/>
       <c r="B263" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D263" s="5">
         <v>1</v>
@@ -4533,7 +4533,7 @@
       <c r="A264" s="4"/>
       <c r="B264" s="4"/>
       <c r="C264" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D264" s="5">
         <v>1</v>
@@ -4543,7 +4543,7 @@
       <c r="A265" s="4"/>
       <c r="B265" s="4"/>
       <c r="C265" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D265" s="5">
         <v>1</v>
@@ -4553,7 +4553,7 @@
       <c r="A266" s="4"/>
       <c r="B266" s="4"/>
       <c r="C266" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D266" s="5">
         <v>1</v>
@@ -4563,7 +4563,7 @@
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D267" s="5">
         <v>1</v>
@@ -4572,10 +4572,10 @@
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" s="4"/>
       <c r="B268" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D268" s="5">
         <v>1</v>
@@ -4585,7 +4585,7 @@
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D269" s="5">
         <v>1</v>
@@ -4595,7 +4595,7 @@
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D270" s="5">
         <v>1</v>
@@ -4605,7 +4605,7 @@
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="7" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D271" s="5">
         <v>1</v>
@@ -4615,7 +4615,7 @@
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D272" s="5">
         <v>1</v>
@@ -4624,10 +4624,10 @@
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="4"/>
       <c r="B273" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C273" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D273" s="5">
         <v>1</v>
@@ -4637,7 +4637,7 @@
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D274" s="5">
         <v>1</v>
@@ -4647,7 +4647,7 @@
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D275" s="5">
         <v>1</v>
@@ -4657,7 +4657,7 @@
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D276" s="5">
         <v>1</v>
@@ -4667,7 +4667,7 @@
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D277" s="5">
         <v>1</v>
@@ -4676,10 +4676,10 @@
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="4"/>
       <c r="B278" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D278" s="5">
         <v>1</v>
@@ -4689,7 +4689,7 @@
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D279" s="5">
         <v>1</v>
@@ -4699,7 +4699,7 @@
       <c r="A280" s="4"/>
       <c r="B280" s="4"/>
       <c r="C280" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D280" s="5">
         <v>1</v>
@@ -4709,7 +4709,7 @@
       <c r="A281" s="4"/>
       <c r="B281" s="4"/>
       <c r="C281" s="7" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D281" s="5">
         <v>1</v>
@@ -4719,7 +4719,7 @@
       <c r="A282" s="4"/>
       <c r="B282" s="4"/>
       <c r="C282" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D282" s="5">
         <v>1</v>
@@ -4728,10 +4728,10 @@
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="4"/>
       <c r="B283" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D283" s="5">
         <v>1</v>
@@ -4741,7 +4741,7 @@
       <c r="A284" s="4"/>
       <c r="B284" s="4"/>
       <c r="C284" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D284" s="5">
         <v>1</v>
@@ -4749,11 +4749,11 @@
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B285" s="4"/>
       <c r="C285" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D285" s="5">
         <v>1</v>
@@ -4763,7 +4763,7 @@
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D286" s="5">
         <v>1</v>
@@ -4773,7 +4773,7 @@
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D287" s="5">
         <v>3</v>
@@ -4783,7 +4783,7 @@
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D288" s="5">
         <v>1</v>
@@ -4791,13 +4791,13 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C289" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D289" s="5">
         <v>1</v>
@@ -4807,7 +4807,7 @@
       <c r="A290" s="4"/>
       <c r="B290" s="4"/>
       <c r="C290" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D290" s="5">
         <v>1</v>
@@ -4817,7 +4817,7 @@
       <c r="A291" s="4"/>
       <c r="B291" s="4"/>
       <c r="C291" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D291" s="5">
         <v>1</v>
@@ -4827,7 +4827,7 @@
       <c r="A292" s="4"/>
       <c r="B292" s="4"/>
       <c r="C292" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D292" s="5">
         <v>1</v>
@@ -4837,7 +4837,7 @@
       <c r="A293" s="4"/>
       <c r="B293" s="4"/>
       <c r="C293" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D293" s="5">
         <v>1</v>
@@ -4847,7 +4847,7 @@
       <c r="A294" s="4"/>
       <c r="B294" s="4"/>
       <c r="C294" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D294" s="5">
         <v>1</v>
@@ -4857,7 +4857,7 @@
       <c r="A295" s="4"/>
       <c r="B295" s="4"/>
       <c r="C295" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D295" s="5">
         <v>1</v>
@@ -4867,7 +4867,7 @@
       <c r="A296" s="4"/>
       <c r="B296" s="4"/>
       <c r="C296" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D296" s="5">
         <v>1</v>
@@ -4877,7 +4877,7 @@
       <c r="A297" s="4"/>
       <c r="B297" s="4"/>
       <c r="C297" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D297" s="5">
         <v>1</v>
@@ -4886,10 +4886,10 @@
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="4"/>
       <c r="B298" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C298" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D298" s="5">
         <v>1</v>
@@ -4899,7 +4899,7 @@
       <c r="A299" s="4"/>
       <c r="B299" s="4"/>
       <c r="C299" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D299" s="5">
         <v>1</v>
@@ -4909,7 +4909,7 @@
       <c r="A300" s="4"/>
       <c r="B300" s="4"/>
       <c r="C300" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D300" s="5">
         <v>1</v>
@@ -4919,7 +4919,7 @@
       <c r="A301" s="4"/>
       <c r="B301" s="4"/>
       <c r="C301" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D301" s="5">
         <v>1</v>
@@ -4929,7 +4929,7 @@
       <c r="A302" s="4"/>
       <c r="B302" s="4"/>
       <c r="C302" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D302" s="5">
         <v>1</v>
@@ -4939,7 +4939,7 @@
       <c r="A303" s="4"/>
       <c r="B303" s="4"/>
       <c r="C303" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D303" s="5">
         <v>1</v>
@@ -4949,7 +4949,7 @@
       <c r="A304" s="4"/>
       <c r="B304" s="4"/>
       <c r="C304" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D304" s="5">
         <v>1</v>
@@ -4959,7 +4959,7 @@
       <c r="A305" s="4"/>
       <c r="B305" s="4"/>
       <c r="C305" s="7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D305" s="5">
         <v>1</v>
@@ -4969,7 +4969,7 @@
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D306" s="5">
         <v>1</v>
@@ -4979,7 +4979,7 @@
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D307" s="5">
         <v>1</v>
@@ -4989,7 +4989,7 @@
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D308" s="5">
         <v>1</v>
@@ -4999,7 +4999,7 @@
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D309" s="5">
         <v>1</v>
@@ -5009,7 +5009,7 @@
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D310" s="5">
         <v>1</v>
@@ -5019,7 +5019,7 @@
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D311" s="5">
         <v>1</v>
@@ -5029,7 +5029,7 @@
       <c r="A312" s="4"/>
       <c r="B312" s="4"/>
       <c r="C312" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D312" s="5">
         <v>1</v>
@@ -5039,7 +5039,7 @@
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D313" s="5">
         <v>1</v>
@@ -5049,7 +5049,7 @@
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D314" s="5">
         <v>1</v>
@@ -5059,7 +5059,7 @@
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D315" s="5">
         <v>1</v>
@@ -5069,7 +5069,7 @@
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D316" s="5">
         <v>1</v>
@@ -5079,7 +5079,7 @@
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D317" s="5">
         <v>1</v>
@@ -5089,7 +5089,7 @@
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D318" s="5">
         <v>1</v>
@@ -5099,7 +5099,7 @@
       <c r="A319" s="4"/>
       <c r="B319" s="4"/>
       <c r="C319" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D319" s="5">
         <v>1</v>
@@ -5109,7 +5109,7 @@
       <c r="A320" s="4"/>
       <c r="B320" s="4"/>
       <c r="C320" s="7" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D320" s="5">
         <v>1</v>
@@ -5119,7 +5119,7 @@
       <c r="A321" s="4"/>
       <c r="B321" s="4"/>
       <c r="C321" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D321" s="5">
         <v>1</v>
@@ -5127,13 +5127,13 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C322" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D322" s="5">
         <v>1</v>
@@ -5143,7 +5143,7 @@
       <c r="A323" s="4"/>
       <c r="B323" s="4"/>
       <c r="C323" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D323" s="5">
         <v>1</v>
@@ -5153,7 +5153,7 @@
       <c r="A324" s="4"/>
       <c r="B324" s="4"/>
       <c r="C324" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D324" s="5">
         <v>1</v>
@@ -5163,7 +5163,7 @@
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D325" s="5">
         <v>1</v>
@@ -5173,7 +5173,7 @@
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D326" s="5">
         <v>1</v>
@@ -5183,7 +5183,7 @@
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D327" s="5">
         <v>1</v>
@@ -5193,7 +5193,7 @@
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D328" s="5">
         <v>1</v>
@@ -5203,7 +5203,7 @@
       <c r="A329" s="4"/>
       <c r="B329" s="4"/>
       <c r="C329" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D329" s="5">
         <v>1</v>
@@ -5213,7 +5213,7 @@
       <c r="A330" s="4"/>
       <c r="B330" s="4"/>
       <c r="C330" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D330" s="5">
         <v>1</v>
@@ -5223,7 +5223,7 @@
       <c r="A331" s="4"/>
       <c r="B331" s="4"/>
       <c r="C331" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D331" s="5">
         <v>1</v>
@@ -5233,7 +5233,7 @@
       <c r="A332" s="4"/>
       <c r="B332" s="4"/>
       <c r="C332" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D332" s="5">
         <v>1</v>
@@ -5243,7 +5243,7 @@
       <c r="A333" s="4"/>
       <c r="B333" s="4"/>
       <c r="C333" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D333" s="5">
         <v>1</v>
@@ -5252,10 +5252,10 @@
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" s="4"/>
       <c r="B334" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C334" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D334" s="5">
         <v>1</v>
@@ -5265,7 +5265,7 @@
       <c r="A335" s="4"/>
       <c r="B335" s="4"/>
       <c r="C335" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D335" s="5">
         <v>1</v>
@@ -5275,7 +5275,7 @@
       <c r="A336" s="4"/>
       <c r="B336" s="4"/>
       <c r="C336" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D336" s="5">
         <v>1</v>
@@ -5285,7 +5285,7 @@
       <c r="A337" s="4"/>
       <c r="B337" s="4"/>
       <c r="C337" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D337" s="5">
         <v>1</v>
@@ -5295,7 +5295,7 @@
       <c r="A338" s="4"/>
       <c r="B338" s="4"/>
       <c r="C338" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D338" s="5">
         <v>1</v>
@@ -5305,7 +5305,7 @@
       <c r="A339" s="4"/>
       <c r="B339" s="4"/>
       <c r="C339" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D339" s="5">
         <v>1</v>
@@ -5315,7 +5315,7 @@
       <c r="A340" s="4"/>
       <c r="B340" s="4"/>
       <c r="C340" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D340" s="5">
         <v>1</v>
@@ -5325,7 +5325,7 @@
       <c r="A341" s="4"/>
       <c r="B341" s="4"/>
       <c r="C341" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D341" s="5">
         <v>1</v>
@@ -5335,7 +5335,7 @@
       <c r="A342" s="4"/>
       <c r="B342" s="4"/>
       <c r="C342" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D342" s="5">
         <v>1</v>
@@ -5345,7 +5345,7 @@
       <c r="A343" s="4"/>
       <c r="B343" s="4"/>
       <c r="C343" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D343" s="5">
         <v>1</v>
@@ -5355,7 +5355,7 @@
       <c r="A344" s="4"/>
       <c r="B344" s="4"/>
       <c r="C344" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D344" s="5">
         <v>1</v>
@@ -5365,7 +5365,7 @@
       <c r="A345" s="4"/>
       <c r="B345" s="4"/>
       <c r="C345" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D345" s="5">
         <v>1</v>
@@ -5373,13 +5373,13 @@
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C346" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D346" s="5">
         <v>1</v>
@@ -5389,7 +5389,7 @@
       <c r="A347" s="4"/>
       <c r="B347" s="4"/>
       <c r="C347" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D347" s="5">
         <v>1</v>
@@ -5399,7 +5399,7 @@
       <c r="A348" s="4"/>
       <c r="B348" s="4"/>
       <c r="C348" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D348" s="5">
         <v>1</v>
@@ -5409,7 +5409,7 @@
       <c r="A349" s="4"/>
       <c r="B349" s="4"/>
       <c r="C349" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D349" s="5">
         <v>1</v>
@@ -5419,7 +5419,7 @@
       <c r="A350" s="4"/>
       <c r="B350" s="4"/>
       <c r="C350" s="7" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D350" s="5">
         <v>1</v>
@@ -5429,7 +5429,7 @@
       <c r="A351" s="4"/>
       <c r="B351" s="4"/>
       <c r="C351" s="7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D351" s="5">
         <v>1</v>
@@ -5439,7 +5439,7 @@
       <c r="A352" s="4"/>
       <c r="B352" s="4"/>
       <c r="C352" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D352" s="5">
         <v>1</v>
@@ -5449,7 +5449,7 @@
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D353" s="5">
         <v>1</v>
@@ -5458,10 +5458,10 @@
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" s="4"/>
       <c r="B354" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C354" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D354" s="5">
         <v>1</v>
@@ -5471,7 +5471,7 @@
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D355" s="5">
         <v>1</v>
@@ -5481,7 +5481,7 @@
       <c r="A356" s="4"/>
       <c r="B356" s="4"/>
       <c r="C356" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D356" s="5">
         <v>1</v>
@@ -5491,7 +5491,7 @@
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D357" s="5">
         <v>1</v>
@@ -5501,7 +5501,7 @@
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="7" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D358" s="5">
         <v>1</v>
@@ -5511,7 +5511,7 @@
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
       <c r="C359" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D359" s="5">
         <v>1</v>
@@ -5521,7 +5521,7 @@
       <c r="A360" s="4"/>
       <c r="B360" s="4"/>
       <c r="C360" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D360" s="5">
         <v>1</v>
@@ -5531,7 +5531,7 @@
       <c r="A361" s="4"/>
       <c r="B361" s="4"/>
       <c r="C361" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D361" s="5">
         <v>1</v>
@@ -5539,11 +5539,11 @@
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B362" s="4"/>
       <c r="C362" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D362" s="5">
         <v>1</v>
@@ -5553,7 +5553,7 @@
       <c r="A363" s="4"/>
       <c r="B363" s="4"/>
       <c r="C363" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D363" s="5">
         <v>1</v>
@@ -5563,7 +5563,7 @@
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D364" s="5">
         <v>1</v>
@@ -5573,7 +5573,7 @@
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D365" s="5">
         <v>1</v>
@@ -5583,7 +5583,7 @@
       <c r="A366" s="4"/>
       <c r="B366" s="4"/>
       <c r="C366" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D366" s="5">
         <v>1</v>
@@ -5593,7 +5593,7 @@
       <c r="A367" s="4"/>
       <c r="B367" s="4"/>
       <c r="C367" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D367" s="5">
         <v>1</v>
@@ -5601,11 +5601,11 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B368" s="4"/>
       <c r="C368" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D368" s="5">
         <v>1</v>
@@ -5615,7 +5615,7 @@
       <c r="A369" s="4"/>
       <c r="B369" s="4"/>
       <c r="C369" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D369" s="5">
         <v>1</v>
@@ -5625,7 +5625,7 @@
       <c r="A370" s="4"/>
       <c r="B370" s="4"/>
       <c r="C370" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D370" s="5">
         <v>1</v>
@@ -5635,7 +5635,7 @@
       <c r="A371" s="4"/>
       <c r="B371" s="4"/>
       <c r="C371" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D371" s="5">
         <v>1</v>
@@ -5904,11 +5904,11 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3">
         <v>2</v>
@@ -5916,11 +5916,11 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="3">
         <v>2</v>
@@ -5928,11 +5928,11 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>

--- a/assets/templates.xlsx
+++ b/assets/templates.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Claude Code\Auftragsdoku FlexPos NFK + BBA\_deploy\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Claude Code\Auftragsdoku FlexPos NFK + BBA\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86126735-770B-4CF4-B3D0-BFF800B080C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9AA12BD-B44E-44AE-A1ED-90ACD41252EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13380" yWindow="6060" windowWidth="25125" windowHeight="14145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NFK Vollverkabelung 3x43HE" sheetId="1" r:id="rId1"/>
